--- a/finalVersion/Results.xlsx
+++ b/finalVersion/Results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="48">
   <si>
     <t>Number</t>
   </si>
@@ -52,21 +52,18 @@
     <t>*</t>
   </si>
   <si>
-    <t>*文件丢失，TBD</t>
+    <t>*代码功能已验证过，但output file过大输出不了（&gt;1024lines）</t>
   </si>
   <si>
     <t>Layer addition 416x416x3</t>
   </si>
   <si>
-    <t>*TBD</t>
+    <t>*框架搭出来了，但实际做不了。问题1，calc的operand2位宽不够。问题2，循环嵌套怎么做？可以展开但仍需解决问题1。</t>
   </si>
   <si>
     <t>ReLU 416x416</t>
   </si>
   <si>
-    <t>*代码功能已验证过，但output file过大输出不了（&gt;1024lines）</t>
-  </si>
-  <si>
     <t>Batch normalization 416x416</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
   </si>
   <si>
     <t>Layer addition 208x208x16</t>
-  </si>
-  <si>
-    <t>*框架搭出来了，但实际做不了。问题1，calc的operand2位宽不够。问题2，循环嵌套怎么做？可以展开但仍需解决问题1。</t>
   </si>
   <si>
     <t>ReLU 208x208</t>
@@ -836,7 +830,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -856,24 +850,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1250,16 +1226,16 @@
       <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>6</v>
+      <c r="D2" s="7">
+        <v>412</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1273,8 +1249,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1284,33 +1260,33 @@
         <v>104</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="7">
+        <v>149</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="8"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="13">
-        <v>149</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="14"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="15">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>6</v>
@@ -1319,18 +1295,18 @@
         <v>140</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="14"/>
+      <c r="A8" s="8"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="16">
+      <c r="A9" s="10">
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6</v>
@@ -1339,28 +1315,28 @@
         <v>222</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="16"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="10"/>
+      <c r="B11" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="16"/>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>6</v>
@@ -1369,13 +1345,13 @@
         <v>106</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="16"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>6</v>
@@ -1384,18 +1360,18 @@
         <v>145</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="14"/>
+      <c r="A13" s="8"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="17">
+      <c r="A14" s="11">
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2">
         <v>46337</v>
@@ -1405,14 +1381,14 @@
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="18"/>
+      <c r="A15" s="12"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="16">
+      <c r="A16" s="10">
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="2">
         <v>103076</v>
@@ -1422,24 +1398,24 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="16"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="10"/>
+      <c r="B18" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="16"/>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C18" s="2">
         <v>13420</v>
@@ -1449,9 +1425,9 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="16"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2">
         <v>14577</v>
@@ -1461,14 +1437,14 @@
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="14"/>
+      <c r="A20" s="8"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="15">
+      <c r="A21" s="9">
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C21" s="2">
         <v>10858</v>
@@ -1478,14 +1454,14 @@
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="19"/>
+      <c r="A22" s="13"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="16">
+      <c r="A23" s="10">
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2">
         <v>26437</v>
@@ -1495,9 +1471,9 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="16"/>
+      <c r="A24" s="10"/>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2">
         <v>175566</v>
@@ -1507,9 +1483,9 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="16"/>
+      <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2">
         <v>2726</v>
@@ -1519,9 +1495,9 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="16"/>
+      <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2">
         <v>2756</v>
@@ -1531,14 +1507,14 @@
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="14"/>
+      <c r="A27" s="8"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="15">
+      <c r="A28" s="9">
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2">
         <v>2742</v>
@@ -1548,14 +1524,14 @@
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="19"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="16">
+      <c r="A30" s="10">
         <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C30" s="2">
         <v>6141</v>
@@ -1565,9 +1541,9 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="16"/>
+      <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2">
         <v>90182</v>
@@ -1577,9 +1553,9 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="16"/>
+      <c r="A32" s="10"/>
       <c r="B32" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2">
         <v>725</v>
@@ -1589,9 +1565,9 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="16"/>
+      <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C33" s="2">
         <v>727</v>
@@ -1601,14 +1577,14 @@
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="14"/>
+      <c r="A34" s="8"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="15">
+      <c r="A35" s="9">
         <v>10</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C35" s="2">
         <v>711</v>
@@ -1618,14 +1594,14 @@
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="19"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="16">
+      <c r="A37" s="10">
         <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C37" s="2">
         <v>1571</v>
@@ -1635,9 +1611,9 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="16"/>
+      <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C38" s="2">
         <v>46866</v>
@@ -1647,9 +1623,9 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="16"/>
+      <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C39" s="2">
         <v>192</v>
@@ -1659,9 +1635,9 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="16"/>
+      <c r="A40" s="10"/>
       <c r="B40" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C40" s="2">
         <v>220</v>
@@ -1671,14 +1647,14 @@
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="19"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="15">
+      <c r="A42" s="9">
         <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C42" s="2">
         <v>610</v>
@@ -1688,11 +1664,11 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="16">
+      <c r="A44" s="10">
         <v>13</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C44" s="2">
         <v>1571</v>
@@ -1702,9 +1678,9 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="16"/>
+      <c r="A45" s="10"/>
       <c r="B45" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C45" s="2">
         <v>93458</v>
@@ -1714,9 +1690,9 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="16"/>
+      <c r="A46" s="10"/>
       <c r="B46" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C46" s="2">
         <v>192</v>
@@ -1726,9 +1702,9 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="16"/>
+      <c r="A47" s="10"/>
       <c r="B47" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="2">
         <v>220</v>
@@ -1738,14 +1714,14 @@
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="14"/>
+      <c r="A48" s="8"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="16">
+      <c r="A49" s="10">
         <v>14</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -1754,18 +1730,18 @@
         <v>6</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="14"/>
+      <c r="A50" s="8"/>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="16">
+      <c r="A51" s="10">
         <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C51" s="2">
         <v>1571</v>
@@ -1775,9 +1751,9 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="16"/>
+      <c r="A52" s="10"/>
       <c r="B52" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C52" s="2">
         <v>46866</v>
@@ -1787,9 +1763,9 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="16"/>
+      <c r="A53" s="10"/>
       <c r="B53" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C53" s="2">
         <v>192</v>
@@ -1799,9 +1775,9 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="16"/>
+      <c r="A54" s="10"/>
       <c r="B54" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C54" s="2">
         <v>220</v>
@@ -1811,91 +1787,91 @@
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="14"/>
+      <c r="A55" s="8"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="16">
+      <c r="A56" s="10">
         <v>16</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="10">
+        <v>17</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="8"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="14">
+        <v>18</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" s="1" t="s">
+      <c r="C60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="16">
-        <v>17</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="14"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="20">
-        <v>18</v>
-      </c>
-      <c r="B60" s="1" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" s="8"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="14">
+        <v>19</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="C62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="14"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="20">
-        <v>19</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="14"/>
+      <c r="A63" s="8"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="16">
+      <c r="A64" s="10">
         <v>20</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C64" s="2">
         <v>6141</v>
@@ -1905,9 +1881,9 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="16"/>
+      <c r="A65" s="10"/>
       <c r="B65" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C65" s="2">
         <v>269894</v>
@@ -1917,9 +1893,9 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="16"/>
+      <c r="A66" s="10"/>
       <c r="B66" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C66" s="2">
         <v>725</v>
@@ -1929,9 +1905,9 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="16"/>
+      <c r="A67" s="10"/>
       <c r="B67" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C67" s="2">
         <v>727</v>
@@ -1941,11 +1917,11 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="16">
+      <c r="A69" s="10">
         <v>21</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>6</v>
@@ -1954,7 +1930,7 @@
         <v>6</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
